--- a/output/pdf_financials_xlsx/CPTR.xlsx
+++ b/output/pdf_financials_xlsx/CPTR.xlsx
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>25.526651</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>17.975071</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>16.647424</v>
+        <v>-8.879227</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-1.037486</v>
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.164881</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.420928</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.345545</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-13.738516</v>
+        <v>-13.573635</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-12.253895</v>
+        <v>-12.674823</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.699693</v>
+        <v>7.354148</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.771472</v>
+        <v>-10.606591</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9.658552</v>
+        <v>-10.07948</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7.699693</v>
+        <v>7.354148</v>
       </c>
     </row>
     <row r="30">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-23.45116838568325</v>
+        <v>-23.09219682686568</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-26.27034101131606</v>
+        <v>-27.41522505824268</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-2.288986</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-2.06476</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-2.288986</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-2.06476</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -4575,7 +4575,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>-2.288986</v>
       </c>
@@ -5604,7 +5608,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6424,7 +6428,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -6521,14 +6525,14 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>-25.526651</v>
+        <v>25.526651</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>-17.554143</v>
+        <v>17.554143</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CPTR.xlsx
+++ b/output/pdf_financials_xlsx/CPTR.xlsx
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.967044</v>
+        <v>0.8204129999999999</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2.595343</v>
+        <v>0.829381</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.606591</v>
+        <v>-12.753222</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-10.07948</v>
+        <v>-11.845442</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>7.354148</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-23.09219682686568</v>
+        <v>-27.76574609134203</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-27.41522505824268</v>
+        <v>-32.2184734077909</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">

--- a/output/pdf_financials_xlsx/CPTR.xlsx
+++ b/output/pdf_financials_xlsx/CPTR.xlsx
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>1.159432</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.859054</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -4172,7 +4172,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -5222,7 +5226,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>1.159432</v>
       </c>
@@ -6089,7 +6097,11 @@
           <t>Deferred income tax recovery (Note 20)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -6771,7 +6783,11 @@
           <t>Deferred income tax recovery (Note 21)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
         <v>0.933233</v>
       </c>
